--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_31-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_31-01-2026.xlsx
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>£35.65</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Max retries exceeded with url: /products/625mm-celotex-pl4050-pir-insulated-plasterboard-2400mm-x-1200mm-625mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£45.40</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Max retries exceeded with url: /products/celotex-cw4000-cavity-wall-boards?variant=42844829909229 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,275.65</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
